--- a/results/q4_output/有效容量分析.xlsx
+++ b/results/q4_output/有效容量分析.xlsx
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>11240</v>
+        <v>11160</v>
       </c>
       <c r="F83" t="n">
-        <v>12920</v>
+        <v>12828</v>
       </c>
       <c r="G83" t="n">
         <v>14.94</v>

--- a/results/q4_output/有效容量分析.xlsx
+++ b/results/q4_output/有效容量分析.xlsx
@@ -493,10 +493,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F2" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G2" t="n">
         <v>14.94</v>
@@ -526,10 +526,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F3" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G3" t="n">
         <v>14.94</v>
@@ -559,10 +559,10 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F4" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G4" t="n">
         <v>14.94</v>
@@ -588,7 +588,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -621,14 +621,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F6" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G6" t="n">
         <v>14.94</v>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F7" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G7" t="n">
         <v>14.94</v>
@@ -687,14 +687,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F8" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G8" t="n">
         <v>14.94</v>
@@ -720,14 +720,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5600</v>
+        <v>7020</v>
       </c>
       <c r="F9" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
       <c r="G9" t="n">
         <v>14.94</v>
@@ -753,14 +753,14 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>3840</v>
+        <v>3740</v>
       </c>
       <c r="F10" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G10" t="n">
         <v>14.94</v>
@@ -786,14 +786,14 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5160</v>
+        <v>6600</v>
       </c>
       <c r="F11" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
       <c r="G11" t="n">
         <v>14.94</v>
@@ -823,10 +823,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F12" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G12" t="n">
         <v>14.94</v>
@@ -856,10 +856,10 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F13" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G13" t="n">
         <v>14.94</v>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F14" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G14" t="n">
         <v>14.94</v>
@@ -918,7 +918,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -951,14 +951,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F16" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G16" t="n">
         <v>14.94</v>
@@ -988,10 +988,10 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F17" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G17" t="n">
         <v>14.94</v>
@@ -1017,14 +1017,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F18" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G18" t="n">
         <v>14.94</v>
@@ -1050,14 +1050,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5600</v>
+        <v>7120</v>
       </c>
       <c r="F19" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G19" t="n">
         <v>14.94</v>
@@ -1083,14 +1083,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3840</v>
+        <v>3740</v>
       </c>
       <c r="F20" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G20" t="n">
         <v>14.94</v>
@@ -1116,14 +1116,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5160</v>
+        <v>6700</v>
       </c>
       <c r="F21" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
       <c r="G21" t="n">
         <v>14.94</v>
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F22" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G22" t="n">
         <v>14.94</v>
@@ -1186,10 +1186,10 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F23" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G23" t="n">
         <v>14.94</v>
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F24" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G24" t="n">
         <v>14.94</v>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1281,14 +1281,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F26" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G26" t="n">
         <v>14.94</v>
@@ -1318,10 +1318,10 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F27" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G27" t="n">
         <v>14.94</v>
@@ -1347,14 +1347,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F28" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G28" t="n">
         <v>14.94</v>
@@ -1380,14 +1380,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5600</v>
+        <v>7220</v>
       </c>
       <c r="F29" t="n">
-        <v>6437</v>
+        <v>8299</v>
       </c>
       <c r="G29" t="n">
         <v>14.94</v>
@@ -1413,14 +1413,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>3840</v>
+        <v>3740</v>
       </c>
       <c r="F30" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G30" t="n">
         <v>14.94</v>
@@ -1446,14 +1446,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5160</v>
+        <v>6800</v>
       </c>
       <c r="F31" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
       <c r="G31" t="n">
         <v>14.94</v>
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F32" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G32" t="n">
         <v>14.94</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F33" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G33" t="n">
         <v>14.94</v>
@@ -1549,10 +1549,10 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F34" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G34" t="n">
         <v>14.94</v>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1611,14 +1611,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F36" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G36" t="n">
         <v>14.94</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F37" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G37" t="n">
         <v>14.94</v>
@@ -1677,14 +1677,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F38" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G38" t="n">
         <v>14.94</v>
@@ -1710,14 +1710,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5600</v>
+        <v>7020</v>
       </c>
       <c r="F39" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
       <c r="G39" t="n">
         <v>14.94</v>
@@ -1743,14 +1743,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3840</v>
+        <v>3740</v>
       </c>
       <c r="F40" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G40" t="n">
         <v>14.94</v>
@@ -1776,14 +1776,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5160</v>
+        <v>6600</v>
       </c>
       <c r="F41" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
       <c r="G41" t="n">
         <v>14.94</v>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F42" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G42" t="n">
         <v>14.94</v>
@@ -1846,10 +1846,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F43" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G43" t="n">
         <v>14.94</v>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F44" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G44" t="n">
         <v>14.94</v>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -1941,14 +1941,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F46" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G46" t="n">
         <v>14.94</v>
@@ -1978,10 +1978,10 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F47" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G47" t="n">
         <v>14.94</v>
@@ -2007,14 +2007,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F48" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G48" t="n">
         <v>14.94</v>
@@ -2040,14 +2040,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5600</v>
+        <v>7120</v>
       </c>
       <c r="F49" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G49" t="n">
         <v>14.94</v>
@@ -2073,14 +2073,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3840</v>
+        <v>3740</v>
       </c>
       <c r="F50" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G50" t="n">
         <v>14.94</v>
@@ -2106,14 +2106,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5160</v>
+        <v>6700</v>
       </c>
       <c r="F51" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
       <c r="G51" t="n">
         <v>14.94</v>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F52" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G52" t="n">
         <v>14.94</v>
@@ -2176,10 +2176,10 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F53" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G53" t="n">
         <v>14.94</v>
@@ -2209,10 +2209,10 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F54" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G54" t="n">
         <v>14.94</v>
@@ -2238,7 +2238,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2271,14 +2271,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F56" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G56" t="n">
         <v>14.94</v>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F57" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G57" t="n">
         <v>14.94</v>
@@ -2337,14 +2337,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F58" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G58" t="n">
         <v>14.94</v>
@@ -2370,14 +2370,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5600</v>
+        <v>7120</v>
       </c>
       <c r="F59" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G59" t="n">
         <v>14.94</v>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2436,14 +2436,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5160</v>
+        <v>6800</v>
       </c>
       <c r="F61" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
       <c r="G61" t="n">
         <v>14.94</v>
@@ -2473,10 +2473,10 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F62" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G62" t="n">
         <v>14.94</v>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F63" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G63" t="n">
         <v>14.94</v>
@@ -2539,10 +2539,10 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F64" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G64" t="n">
         <v>14.94</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E65" t="n">
@@ -2601,14 +2601,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F66" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G66" t="n">
         <v>14.94</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F67" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G67" t="n">
         <v>14.94</v>
@@ -2667,14 +2667,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F68" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G68" t="n">
         <v>14.94</v>
@@ -2700,14 +2700,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5600</v>
+        <v>7020</v>
       </c>
       <c r="F69" t="n">
-        <v>6437</v>
+        <v>8069</v>
       </c>
       <c r="G69" t="n">
         <v>14.94</v>
@@ -2733,14 +2733,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3840</v>
+        <v>3740</v>
       </c>
       <c r="F70" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G70" t="n">
         <v>14.94</v>
@@ -2766,14 +2766,14 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5160</v>
+        <v>6600</v>
       </c>
       <c r="F71" t="n">
-        <v>5931</v>
+        <v>7586</v>
       </c>
       <c r="G71" t="n">
         <v>14.94</v>
@@ -2803,10 +2803,10 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F72" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G72" t="n">
         <v>14.94</v>
@@ -2836,10 +2836,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F73" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G73" t="n">
         <v>14.94</v>
@@ -2869,10 +2869,10 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F74" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G74" t="n">
         <v>14.94</v>
@@ -2898,7 +2898,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -2931,14 +2931,14 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F76" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G76" t="n">
         <v>14.94</v>
@@ -2968,10 +2968,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F77" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G77" t="n">
         <v>14.94</v>
@@ -2997,14 +2997,14 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F78" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G78" t="n">
         <v>14.94</v>
@@ -3030,14 +3030,14 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5600</v>
+        <v>7120</v>
       </c>
       <c r="F79" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G79" t="n">
         <v>14.94</v>
@@ -3063,14 +3063,14 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3840</v>
+        <v>3740</v>
       </c>
       <c r="F80" t="n">
-        <v>4414</v>
+        <v>4299</v>
       </c>
       <c r="G80" t="n">
         <v>14.94</v>
@@ -3096,14 +3096,14 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5160</v>
+        <v>6700</v>
       </c>
       <c r="F81" t="n">
-        <v>5931</v>
+        <v>7701</v>
       </c>
       <c r="G81" t="n">
         <v>14.94</v>
@@ -3133,10 +3133,10 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>12080</v>
+        <v>12040</v>
       </c>
       <c r="F82" t="n">
-        <v>13885</v>
+        <v>13839</v>
       </c>
       <c r="G82" t="n">
         <v>14.94</v>
@@ -3166,10 +3166,10 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>11160</v>
+        <v>11100</v>
       </c>
       <c r="F83" t="n">
-        <v>12828</v>
+        <v>12759</v>
       </c>
       <c r="G83" t="n">
         <v>14.94</v>
@@ -3199,10 +3199,10 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>9400</v>
+        <v>9240</v>
       </c>
       <c r="F84" t="n">
-        <v>10805</v>
+        <v>10621</v>
       </c>
       <c r="G84" t="n">
         <v>14.94</v>
@@ -3228,7 +3228,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>桥沟街道</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -3261,14 +3261,14 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>桥沟街道</t>
+          <t>枣园街道</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>7220</v>
+        <v>7520</v>
       </c>
       <c r="F86" t="n">
-        <v>8299</v>
+        <v>8644</v>
       </c>
       <c r="G86" t="n">
         <v>14.94</v>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>9040</v>
+        <v>8960</v>
       </c>
       <c r="F87" t="n">
-        <v>10391</v>
+        <v>10299</v>
       </c>
       <c r="G87" t="n">
         <v>14.94</v>
@@ -3327,14 +3327,14 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>柳林镇</t>
+          <t>河庄坪镇</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4320</v>
+        <v>4660</v>
       </c>
       <c r="F88" t="n">
-        <v>4966</v>
+        <v>5356</v>
       </c>
       <c r="G88" t="n">
         <v>14.94</v>
@@ -3360,14 +3360,14 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>河庄坪镇</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5600</v>
+        <v>7120</v>
       </c>
       <c r="F89" t="n">
-        <v>6437</v>
+        <v>8184</v>
       </c>
       <c r="G89" t="n">
         <v>14.94</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>姚店镇</t>
+          <t>万花山镇</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3426,14 +3426,14 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>李渠镇</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5160</v>
+        <v>6800</v>
       </c>
       <c r="F91" t="n">
-        <v>5931</v>
+        <v>7816</v>
       </c>
       <c r="G91" t="n">
         <v>14.94</v>
